--- a/reports/播客监控日报_2026-03-17.xlsx
+++ b/reports/播客监控日报_2026-03-17.xlsx
@@ -439,21 +439,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -464,55 +465,60 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>基金公司</t>
+          <t>分类</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>机构名称</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>订阅数</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>最新单集名称</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>最新单集上线日期</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>最新单集播放数量</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>最新单集评论数</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>最新单集点赞数</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>最新单集收藏数</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>互动指标(点赞+收藏)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>最新单集时长</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>抓取时间</t>
         </is>
@@ -524,53 +530,62 @@
           <t>无人知晓</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="3" t="n">
-        <v>1568269</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>独立节目</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>孟岩</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>1570731</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>E45 孟岩对话李继刚：人何以自处</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>2026-03-03</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>376568</t>
-        </is>
-      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>1671</t>
+          <t>387308</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>4475</t>
+          <t>1694</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>4394</t>
+          <t>4586</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
+          <t>9077</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
           <t>3:26:38</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:31:58</t>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:28:34</t>
         </is>
       </c>
     </row>
@@ -582,55 +597,60 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>其他金融机构</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>第一财经</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>732318</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="n">
+        <v>733043</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>商业小样35 | 霍尔木兹海峡上的特殊保险</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>25649</t>
-        </is>
-      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30909</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>110</t>
+          <t>97</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
           <t>11:24</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:31:40</t>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:28:14</t>
         </is>
       </c>
     </row>
@@ -640,53 +660,62 @@
           <t>面基</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="3" t="n">
-        <v>530005</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>站在美股之巅，满眼山雨欲来</t>
-        </is>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>独立节目</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>老钱</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>530809</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>管家里钱，其实和保险公司的思路最像</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>79240</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>6604</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1:27:26</t>
+          <t>84</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17 02:31:42</t>
+          <t>1:19:03</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:28:18</t>
         </is>
       </c>
     </row>
@@ -696,53 +725,62 @@
           <t>起朱楼宴宾客</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="3" t="n">
-        <v>355767</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>独立节目</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>大卫翁</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>356617</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>159.算法的六副面孔：它是如何从处理数据，变成定义我们是谁的</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>2026-03-10</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>29499</t>
-        </is>
-      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>30824</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>156</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>143</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>238</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>1:09:19</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:31:44</t>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:28:20</t>
         </is>
       </c>
     </row>
@@ -754,30 +792,30 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>公募基金</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>华夏基金</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>173402</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="n">
+        <v>173605</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>首届红火播客节科技场：奇点临近，咱能跟上科技浪潮么？</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8734</t>
-        </is>
-      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>10835</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -787,22 +825,27 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>1:10:26</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:30:43</t>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:27:19</t>
         </is>
       </c>
     </row>
@@ -814,42 +857,42 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>其他金融机构</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>中金公司</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
-        <v>145298</v>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="n">
+        <v>145906</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>episode 49｜中金机器人播客 跨维智能贾奎：物理AI、世界模型与具身智能的商业化路径</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>3071</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>3460</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
           <t>25</t>
@@ -857,12 +900,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>1:24:21</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:31:34</t>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:28:10</t>
         </is>
       </c>
     </row>
@@ -872,53 +920,62 @@
           <t>三点下班</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr"/>
-      <c r="C8" s="3" t="n">
-        <v>141317</v>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>独立节目</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>李永浩、星辰</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>141559</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>如何应对下一次危机--附方法论和检查清单</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9183</t>
-        </is>
-      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>15913</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>173</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>198</t>
+          <t>112</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>56:21</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:31:46</t>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:28:22</t>
         </is>
       </c>
     </row>
@@ -930,55 +987,60 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>公募基金</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>雪球财富</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n">
-        <v>122024</v>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="3" t="n">
+        <v>122377</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>AI时代，文科生要触底反弹了？</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>7890</t>
-        </is>
-      </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10798</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
           <t>1:18:08</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:31:30</t>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:28:06</t>
         </is>
       </c>
     </row>
@@ -988,53 +1050,62 @@
           <t>投资ABC｜掌握投资中那些绕不开的知识</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr"/>
-      <c r="C10" s="3" t="n">
-        <v>94134</v>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>独立节目</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>有知有行</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>94404</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>低利率时代，我的定期存款到期了，这笔钱该怎么办？｜我问陈博士 14</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8325</t>
-        </is>
-      </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>11290</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>61</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>55</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>73</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>47:21</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:31:38</t>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:28:16</t>
         </is>
       </c>
     </row>
@@ -1046,55 +1117,60 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>公募基金</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>中欧基金</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n">
-        <v>78138</v>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="3" t="n">
+        <v>78581</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>46.HALO交易爆火：当AI狂奔，市场又开始拥抱“老派”资产</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>2026-03-10</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>10411</t>
-        </is>
-      </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>10948</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
           <t>26:25</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:30:44</t>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:27:20</t>
         </is>
       </c>
     </row>
@@ -1104,53 +1180,62 @@
           <t>钱粮胡同FM</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr"/>
-      <c r="C12" s="3" t="n">
-        <v>74649</v>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>独立节目</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>住在胡同的野人、无聊D、细菌佛</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>74768</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>318.伊朗的昨天</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>18164</t>
-        </is>
-      </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>21455</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>242</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>76</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>142</t>
+          <t>89</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>1:54:25</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:31:52</t>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:28:28</t>
         </is>
       </c>
     </row>
@@ -1160,53 +1245,62 @@
           <t>十分吸引</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr"/>
-      <c r="C13" s="3" t="n">
-        <v>69633</v>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>独立节目</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>石磊</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>70317</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Vol.59 当"失去的30年"叙事终结：我们该如何看待今天的日本？</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11730</t>
-        </is>
-      </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>16118</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>162</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>1:11:36</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:31:50</t>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:28:26</t>
         </is>
       </c>
     </row>
@@ -1218,55 +1312,60 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
+          <t>公募基金</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
           <t>蚂蚁财富</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
-        <v>49557</v>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="3" t="n">
+        <v>49600</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>关于马斯克精心布局，终于把"奇点年"召唤到眼前，这件大事</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>7296</t>
-        </is>
-      </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>7531</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>54</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>1:12:04</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:31:28</t>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:28:04</t>
         </is>
       </c>
     </row>
@@ -1278,55 +1377,60 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>公募基金</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
           <t>富国基金</t>
         </is>
       </c>
-      <c r="C15" s="3" t="n">
-        <v>38253</v>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="3" t="n">
+        <v>38508</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>一周富盘 | “养龙虾”爆火刷屏！头部大厂纷纷入局，AI智能体热潮下，基金该怎么布局？</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>3619</t>
-        </is>
-      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
+          <t>5111</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>142</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
           <t>13:19</t>
         </is>
       </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:30:46</t>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:27:22</t>
         </is>
       </c>
     </row>
@@ -1336,53 +1440,62 @@
           <t>The Wanderers 流浪者</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr"/>
-      <c r="C16" s="3" t="n">
-        <v>32133</v>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>独立节目</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>zjyiran、Jason_NDV、Vincent-Lu</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>32140</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>2028智能危机：人类经济体会崩溃吗？</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>19101</t>
-        </is>
-      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>19320</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>83</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>130</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>1:13:53</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:31:48</t>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:28:24</t>
         </is>
       </c>
     </row>
@@ -1394,40 +1507,40 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
+          <t>公募基金</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
           <t>天弘基金</t>
         </is>
       </c>
-      <c r="C17" s="3" t="n">
-        <v>26907</v>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="3" t="n">
+        <v>26915</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>E35 美伊冲突全球动荡，如何防止钱包烧毁？</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2781</t>
-        </is>
-      </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2917</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1437,12 +1550,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
           <t>33:36</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:30:50</t>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:27:26</t>
         </is>
       </c>
     </row>
@@ -1454,55 +1572,60 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
+          <t>公募基金</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
           <t>华泰证券</t>
         </is>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>22734</v>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>S3E11 | 超越传统“因子工厂”：AGI开启量化投资新时代</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>2025-08-15</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>952</t>
-        </is>
-      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>1:00:39</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:31:26</t>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:28:02</t>
         </is>
       </c>
     </row>
@@ -1514,55 +1637,60 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
+          <t>公募基金</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
           <t>大成基金</t>
         </is>
       </c>
-      <c r="C19" s="3" t="n">
-        <v>20524</v>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="3" t="n">
+        <v>20530</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>18.Seedance出炉，AI视频革命与科技投资新范式</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>2026-02-13</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>7630</t>
-        </is>
-      </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
+          <t>7644</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>176</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>133</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>309</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>44:50</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:30:52</t>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:27:28</t>
         </is>
       </c>
     </row>
@@ -1572,53 +1700,62 @@
           <t>燕妮聊基金</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr"/>
-      <c r="C20" s="3" t="n">
-        <v>17304</v>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>86、往期好播客大推荐</t>
-        </is>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>独立节目</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>燕妮</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>17360</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>87、聊聊那些投资迷思</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>734</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>43:43</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17 02:31:54</t>
+          <t>1:02:01</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:28:30</t>
         </is>
       </c>
     </row>
@@ -1630,55 +1767,60 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
+          <t>公募基金</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
           <t>中金资管</t>
         </is>
       </c>
-      <c r="C21" s="3" t="n">
-        <v>8946</v>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="3" t="n">
+        <v>8959</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>EP135 对话中金公司食品饮料行业首席分析师：当“反向过年”遇上“下沉消费”</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>1092</t>
-        </is>
-      </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
+          <t>1160</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>59:51</t>
         </is>
       </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:31:24</t>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:28:00</t>
         </is>
       </c>
     </row>
@@ -1690,30 +1832,30 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
+          <t>公募基金</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
           <t>德邦基金</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n">
-        <v>8471</v>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>310.一文看懂电力产业：普通投资者必知的行业核心逻辑</t>
-        </is>
+      <c r="D22" s="3" t="n">
+        <v>8491</v>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>311.3月17日财经速递</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>140</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1723,22 +1865,27 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3:08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17 02:31:02</t>
+          <t>4:14</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:27:38</t>
         </is>
       </c>
     </row>
@@ -1750,55 +1897,60 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
+          <t>公募基金</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
           <t>兴全基金</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
-        <v>6961</v>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="3" t="n">
+        <v>6989</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>OpenClaw爆火后，AI发展的2个重点方向</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>2026-03-09</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1274</t>
-        </is>
-      </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>55:15</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:31:20</t>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:27:56</t>
         </is>
       </c>
     </row>
@@ -1810,55 +1962,60 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
+          <t>公募基金</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
           <t>易方达基金</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n">
-        <v>6838</v>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="3" t="n">
+        <v>6840</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>对话三点下班浩哥：他说感谢股市改写了他的人生</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>2026-01-13</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>3205</t>
-        </is>
-      </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
+          <t>3211</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="J24" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>1:42:13</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:31:12</t>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:27:48</t>
         </is>
       </c>
     </row>
@@ -1870,55 +2027,60 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
+          <t>公募基金</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
           <t>国泰基金</t>
         </is>
       </c>
-      <c r="C25" s="3" t="n">
-        <v>6278</v>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="3" t="n">
+        <v>6282</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Vol 27 Z世代的新年消费回忆录</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>4416</t>
-        </is>
-      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4427</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>215</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>53:31</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:31:10</t>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:27:46</t>
         </is>
       </c>
     </row>
@@ -1930,55 +2092,60 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
+          <t>公募基金</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
           <t>嘉实基金</t>
         </is>
       </c>
-      <c r="C26" s="3" t="n">
-        <v>5398</v>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" s="3" t="n">
+        <v>5401</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Ep10.当“一盒内存条=一套房”：这轮半导体行情谁在定价？</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>26328</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
+          <t>26419</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>225</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>295</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>296</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
+          <t>521</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
           <t>1:20:43</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:31:08</t>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:27:44</t>
         </is>
       </c>
     </row>
@@ -1990,55 +2157,60 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
+          <t>公募基金</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
           <t>银华基金</t>
         </is>
       </c>
-      <c r="C27" s="3" t="n">
-        <v>4480</v>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="3" t="n">
+        <v>4481</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>养娃这条路，做好财务规划能省多少弯路？</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>2025-09-17</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>5354</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
+          <t>5358</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="I27" s="2" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="J27" s="2" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>1:12:50</t>
         </is>
       </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:31:14</t>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:27:50</t>
         </is>
       </c>
     </row>
@@ -2050,55 +2222,60 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
+          <t>公募基金</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
           <t>易方达基金</t>
         </is>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>3816</v>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Vol.18 | 越南市场为何快速上涨？——基金经理越南调研感受</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>2025-11-14</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>4694</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>25:02</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:31:16</t>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:27:52</t>
         </is>
       </c>
     </row>
@@ -2110,55 +2287,60 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
+          <t>公募基金</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
           <t>广发基金</t>
         </is>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>3297</v>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>港股科技风起，未来路在何方？| 串台「自由进度条」</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>263</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>55:16</t>
         </is>
       </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:30:54</t>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:27:30</t>
         </is>
       </c>
     </row>
@@ -2170,55 +2352,60 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
+          <t>公募基金</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
           <t>汇添富基金</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>1989</v>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>E20“宠物理财”小课堂：养毛孩子，怎样花钱不心疼？</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>2026-01-07</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>17:57</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:31:18</t>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:27:54</t>
         </is>
       </c>
     </row>
@@ -2230,30 +2417,30 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
+          <t>公募基金</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
           <t>中泰资管</t>
         </is>
       </c>
-      <c r="C31" s="3" t="n">
-        <v>1599</v>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="3" t="n">
+        <v>1603</v>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>E33.田瑀｜研究不必设限，结论宁缺毋滥</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>2026-03-10</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
-      </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>392</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2263,22 +2450,27 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>32:01</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:31:00</t>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:27:36</t>
         </is>
       </c>
     </row>
@@ -2290,30 +2482,30 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
+          <t>公募基金</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
           <t>国投瑞银基金</t>
         </is>
       </c>
-      <c r="C32" s="3" t="n">
-        <v>1494</v>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>EP9.别内耗了，允许自己“知行不合一”</t>
-        </is>
+      <c r="D32" s="3" t="n">
+        <v>1496</v>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>EP10.没有终点的修行：育儿与投资的无限游戏</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>32</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -2323,22 +2515,27 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1:10:07</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2026-03-17 02:31:04</t>
+          <t>1:24:36</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:27:40</t>
         </is>
       </c>
     </row>
@@ -2350,55 +2547,60 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
+          <t>公募基金</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
           <t>财通基金</t>
         </is>
       </c>
-      <c r="C33" s="3" t="n">
-        <v>1307</v>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" s="3" t="n">
+        <v>1306</v>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>一线基金经理闭门分享：AI、有色、出海……2026年的钱往哪里投？</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>1232</t>
-        </is>
-      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="J33" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="J33" s="2" t="inlineStr">
+      <c r="K33" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>1:29:38</t>
         </is>
       </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:30:48</t>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:27:24</t>
         </is>
       </c>
     </row>
@@ -2410,55 +2612,60 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
+          <t>公募基金</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
           <t>鹏华基金</t>
         </is>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>738</v>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Vol 3：新消费浪潮，Z世代用"情绪货币"改写"商业规则"？|元气消费局</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>2025-11-11</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>2882</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>129</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="J34" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
         <is>
           <t>151</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>54:38</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:31:22</t>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:27:58</t>
         </is>
       </c>
     </row>
@@ -2470,19 +2677,19 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
+          <t>其他金融机构</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
           <t>广发证券</t>
         </is>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>481</v>
       </c>
-      <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr"/>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2503,10 +2710,15 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr"/>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:31:36</t>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:28:12</t>
         </is>
       </c>
     </row>
@@ -2518,32 +2730,32 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
+          <t>公募基金</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
           <t>华夏基金</t>
         </is>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>417</v>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>A股开年连跌三周，春节行情还能期待吗？0122</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>2024-01-22</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2561,12 +2773,17 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
           <t>19:20</t>
         </is>
       </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:31:32</t>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:28:08</t>
         </is>
       </c>
     </row>
@@ -2578,32 +2795,32 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
+          <t>公募基金</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
           <t>银华基金</t>
         </is>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>305</v>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Vol 53：银华王丽敏：“周期搭台，成长唱戏”或是未来一段时间A股的主旋律</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2621,12 +2838,17 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
           <t>2:01</t>
         </is>
       </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:30:56</t>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:27:32</t>
         </is>
       </c>
     </row>
@@ -2638,55 +2860,60 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
+          <t>公募基金</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
           <t>中泰资管</t>
         </is>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Vol.5 不上班的日子，跑步、做饭、好好生活</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>1:00:18</t>
         </is>
       </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:30:58</t>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:27:34</t>
         </is>
       </c>
     </row>
@@ -2698,32 +2925,32 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
+          <t>公募基金</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
           <t>国投瑞银基金</t>
         </is>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>0010 段永平《波士堂》访谈：敢为天下后</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>2025-10-07</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>124</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2741,12 +2968,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
           <t>19:39</t>
         </is>
       </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:31:06</t>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:27:42</t>
         </is>
       </c>
     </row>
@@ -2756,17 +2988,21 @@
           <t>听懂掌声</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr"/>
-      <c r="C40" s="3" t="n">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>独立节目</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>天楠</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr"/>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="F40" s="2" t="inlineStr"/>
       <c r="G40" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2787,10 +3023,15 @@
           <t>0</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17 02:31:56</t>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17 22:28:32</t>
         </is>
       </c>
     </row>
